--- a/OT.xlsx
+++ b/OT.xlsx
@@ -1,158 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24701"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SkyTam\Desktop\ChamCong\Code\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077B5FD8-2354-4B7B-A3AC-C073A24EC24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="20211221" sheetId="1" r:id="rId1"/>
+    <sheet name="20211221" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
-  <si>
-    <t>Tăng ca</t>
-  </si>
-  <si>
-    <t>Mã nhân viên</t>
-  </si>
-  <si>
-    <t>Tên nhân viên</t>
-  </si>
-  <si>
-    <t>Bộ Phận</t>
-  </si>
-  <si>
-    <t>Mã thanh toán</t>
-  </si>
-  <si>
-    <t>Thời gian bắt đầu</t>
-  </si>
-  <si>
-    <t>Thời gian kết thúc</t>
-  </si>
-  <si>
-    <t>Áp dụng lý do</t>
-  </si>
-  <si>
-    <t>Áp dụng thời gian</t>
-  </si>
-  <si>
-    <t>Trạng thái phê duyệt</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Nhân viên 9</t>
-  </si>
-  <si>
-    <t>San xuat</t>
-  </si>
-  <si>
-    <t>Xin làm thêm</t>
-  </si>
-  <si>
-    <t>2021-10-01 18:00:00</t>
-  </si>
-  <si>
-    <t>2021-10-01 19:00:00</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:22:08</t>
-  </si>
-  <si>
-    <t>Phê duyệt</t>
-  </si>
-  <si>
-    <t>2021-10-02 18:00:00</t>
-  </si>
-  <si>
-    <t>2021-10-02 23:00:00</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:21:34</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Nhân viên 8</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:19:41</t>
-  </si>
-  <si>
-    <t>2021-10-01 19:30:00</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:19:03</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Nhân viên 10</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:17:47</t>
-  </si>
-  <si>
-    <t>2021-10-01 21:00:00</t>
-  </si>
-  <si>
-    <t>2021-12-19 11:17:09</t>
-  </si>
-  <si>
-    <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -186,35 +80,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -538,237 +501,403 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
-    <col min="6" max="6" width="36.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col width="24.7109375" customWidth="1" min="1" max="1"/>
+    <col width="26.7109375" customWidth="1" min="2" max="2"/>
+    <col width="14.7109375" customWidth="1" min="3" max="3"/>
+    <col width="26.7109375" customWidth="1" min="4" max="4"/>
+    <col width="34.7109375" customWidth="1" min="5" max="5"/>
+    <col width="36.7109375" customWidth="1" min="6" max="6"/>
+    <col width="26.7109375" customWidth="1" min="7" max="7"/>
+    <col width="34.7109375" customWidth="1" min="8" max="8"/>
+    <col width="40.7109375" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+    <row r="1" ht="17.1" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="n"/>
     </row>
-    <row r="2" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tăng ca</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="1"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Mã nhân viên</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Tên nhân viên</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Bộ Phận</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Mã thanh toán</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Thời gian bắt đầu</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Thời gian kết thúc</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Áp dụng lý do</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Áp dụng thời gian</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Trạng thái phê duyệt</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>17</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 9</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J4">
+        <f>hour(F4-E4)</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>day(E4)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 9</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 23:00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J5">
+        <f>hour(F5-E5)</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>day(E5)</f>
+        <v/>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 8</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 23:00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J6">
+        <f>hour(F6-E6)</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>day(E6)</f>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 8</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 19:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J7">
+        <f>hour(F7-E7)</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>day(E7)</f>
+        <v/>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 10</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-02 23:00:00</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J8">
+        <f>hour(F8-E8)</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>day(E8)</f>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Nhân viên 10</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>San xuat</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Xin làm thêm</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>2021-10-01 21:00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Phê duyệt</t>
+        </is>
+      </c>
+      <c r="J9">
+        <f>hour(F9-E9)</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>day(E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="J10">
+        <f>hour(F10-E10)</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>day(E10)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -777,6 +906,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/OT.xlsx
+++ b/OT.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11685" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="20211221" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -18,11 +18,10 @@
   <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -66,6 +65,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -80,36 +88,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -192,44 +192,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -257,31 +257,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -309,23 +292,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -337,166 +303,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -506,406 +448,383 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24.7109375" customWidth="1" min="1" max="1"/>
-    <col width="26.7109375" customWidth="1" min="2" max="2"/>
-    <col width="14.7109375" customWidth="1" min="3" max="3"/>
-    <col width="26.7109375" customWidth="1" min="4" max="4"/>
-    <col width="34.7109375" customWidth="1" min="5" max="5"/>
-    <col width="36.7109375" customWidth="1" min="6" max="6"/>
-    <col width="26.7109375" customWidth="1" min="7" max="7"/>
-    <col width="34.7109375" customWidth="1" min="8" max="8"/>
-    <col width="40.7109375" customWidth="1" min="9" max="9"/>
-  </cols>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" ht="17.1" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="20.25" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
         </is>
       </c>
-      <c r="I1" s="4" t="n"/>
+      <c r="I1" s="3" t="n"/>
     </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="20.25" customHeight="1" s="2">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Tăng ca</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n"/>
+      <c r="I2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Mã nhân viên</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tên nhân viên</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Bộ Phận</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Mã thanh toán</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Thời gian bắt đầu</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Thời gian kết thúc</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Áp dụng lý do</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Áp dụng thời gian</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Trạng thái phê duyệt</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 9</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 18:00:00</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 19:00:00</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J4">
-        <f>hour(F4-E4)</f>
-        <v/>
-      </c>
-      <c r="K4">
-        <f>day(E4)</f>
-        <v/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 9</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 18:00:00</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 23:00:00</t>
         </is>
       </c>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J5">
-        <f>hour(F5-E5)</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>day(E5)</f>
-        <v/>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 8</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 18:00:00</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 23:00:00</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J6">
-        <f>hour(F6-E6)</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>day(E6)</f>
-        <v/>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 8</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 18:00:00</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 19:30:00</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J7">
-        <f>hour(F7-E7)</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>day(E7)</f>
-        <v/>
+      <c r="J7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 10</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 18:00:00</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2021-10-02 23:00:00</t>
         </is>
       </c>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J8">
-        <f>hour(F8-E8)</f>
-        <v/>
-      </c>
-      <c r="K8">
-        <f>day(E8)</f>
-        <v/>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Nhân viên 10</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>San xuat</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Xin làm thêm</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 18:00:00</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2021-10-01 21:00:00</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Phê duyệt</t>
         </is>
       </c>
-      <c r="J9">
-        <f>hour(F9-E9)</f>
-        <v/>
-      </c>
-      <c r="K9">
-        <f>day(E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="J10">
-        <f>hour(F10-E10)</f>
-        <v/>
-      </c>
-      <c r="K10">
-        <f>day(E10)</f>
-        <v/>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>